--- a/BoM/Positional/t1-bom.xlsx
+++ b/BoM/Positional/t1-bom.xlsx
@@ -190,7 +190,7 @@
     <t>1.4000</t>
   </si>
   <si>
-    <t>+5V,GND</t>
+    <t>GND,+5V</t>
   </si>
   <si>
     <t>Default</t>
@@ -289,135 +289,135 @@
     <t>1.7500</t>
   </si>
   <si>
-    <t>+5V,/RESET2</t>
+    <t>/RESET2,+5V</t>
+  </si>
+  <si>
+    <t>RESET2,+5V</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Light emitting diode</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>D2 D3</t>
+  </si>
+  <si>
+    <t>LED_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>LED_SMD</t>
+  </si>
+  <si>
+    <t>t1(2)</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>147.3200</t>
+  </si>
+  <si>
+    <t>-74.9500</t>
+  </si>
+  <si>
+    <t>Net-(D2-A),/RXLED</t>
+  </si>
+  <si>
+    <t>RXLED</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>DC Barrel Jack with an internal switch</t>
+  </si>
+  <si>
+    <t>Barrel_Jack_Switch</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>BarrelJack_CLIFF_FC681465S_SMT_Horizontal</t>
+  </si>
+  <si>
+    <t>Connector_BarrelJack</t>
+  </si>
+  <si>
+    <t>Connector_BarrelJack:BarrelJack_CLIFF_FC681465S_SMT_Horizontal</t>
+  </si>
+  <si>
+    <t>126.1000</t>
+  </si>
+  <si>
+    <t>-81.2000</t>
+  </si>
+  <si>
+    <t>8.0000</t>
+  </si>
+  <si>
+    <t>14.0000</t>
+  </si>
+  <si>
+    <t>,GND,+5V</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Generic connector, double row, 02x03, odd/even pin numbering scheme (row 1 odd numbers, row 2 even numbers), script generated (kicad-library-utils/schlib/autogen/connector/)</t>
+  </si>
+  <si>
+    <t>Conn_02x03_Odd_Even</t>
+  </si>
+  <si>
+    <t>Connector_Generic</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>ICSP1</t>
+  </si>
+  <si>
+    <t>PinHeader_2x03_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2.54mm</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2.54mm:PinHeader_2x03_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>141.1224</t>
+  </si>
+  <si>
+    <t>-97.7646</t>
+  </si>
+  <si>
+    <t>THT</t>
+  </si>
+  <si>
+    <t>4.2400</t>
+  </si>
+  <si>
+    <t>6.7800</t>
+  </si>
+  <si>
+    <t>/SCK2,/MOSI2,GND,/MISO2,+5V,/RESET2</t>
   </si>
   <si>
     <t>RESET2</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Light emitting diode</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>D2 D3</t>
-  </si>
-  <si>
-    <t>LED_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>LED_SMD</t>
-  </si>
-  <si>
-    <t>t1(2)</t>
-  </si>
-  <si>
-    <t>LED_SMD:LED_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>147.3200</t>
-  </si>
-  <si>
-    <t>-74.9500</t>
-  </si>
-  <si>
-    <t>/RXLED,Net-(D2-A)</t>
-  </si>
-  <si>
-    <t>RXLED,Net-(D2-A)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>DC Barrel Jack with an internal switch</t>
-  </si>
-  <si>
-    <t>Barrel_Jack_Switch</t>
-  </si>
-  <si>
-    <t>Connector</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>BarrelJack_CLIFF_FC681465S_SMT_Horizontal</t>
-  </si>
-  <si>
-    <t>Connector_BarrelJack</t>
-  </si>
-  <si>
-    <t>Connector_BarrelJack:BarrelJack_CLIFF_FC681465S_SMT_Horizontal</t>
-  </si>
-  <si>
-    <t>126.1000</t>
-  </si>
-  <si>
-    <t>-81.2000</t>
-  </si>
-  <si>
-    <t>8.0000</t>
-  </si>
-  <si>
-    <t>14.0000</t>
-  </si>
-  <si>
-    <t>,GND,+5V</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Generic connector, double row, 02x03, odd/even pin numbering scheme (row 1 odd numbers, row 2 even numbers), script generated (kicad-library-utils/schlib/autogen/connector/)</t>
-  </si>
-  <si>
-    <t>Conn_02x03_Odd_Even</t>
-  </si>
-  <si>
-    <t>Connector_Generic</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>ICSP1</t>
-  </si>
-  <si>
-    <t>PinHeader_2x03_P2.54mm_Vertical</t>
-  </si>
-  <si>
-    <t>Connector_PinHeader_2.54mm</t>
-  </si>
-  <si>
-    <t>Connector_PinHeader_2.54mm:PinHeader_2x03_P2.54mm_Vertical</t>
-  </si>
-  <si>
-    <t>141.1224</t>
-  </si>
-  <si>
-    <t>-97.7646</t>
-  </si>
-  <si>
-    <t>THT</t>
-  </si>
-  <si>
-    <t>4.2400</t>
-  </si>
-  <si>
-    <t>6.7800</t>
-  </si>
-  <si>
-    <t>+5V,/SCK2,/RESET2,/MISO2,GND,/MOSI2</t>
-  </si>
-  <si>
-    <t>MOSI2</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -454,7 +454,7 @@
     <t>11.8600</t>
   </si>
   <si>
-    <t>Net-(J3-Pin_5),Net-(J3-Pin_1),Net-(J3-Pin_3),Net-(J3-Pin_2),Net-(J3-Pin_4)</t>
+    <t>Net-(J3-Pin_2),Net-(J3-Pin_1),Net-(J3-Pin_3),Net-(J3-Pin_4),Net-(J3-Pin_5)</t>
   </si>
   <si>
     <t>9</t>
@@ -487,7 +487,7 @@
     <t>14.4000</t>
   </si>
   <si>
-    <t>Net-(J6-Pin_5),Net-(J6-Pin_3),Net-(J6-Pin_1),Net-(J6-Pin_6),Net-(J6-Pin_2),Net-(J6-Pin_4)</t>
+    <t>Net-(J6-Pin_6),Net-(J6-Pin_2),Net-(J6-Pin_3),Net-(J6-Pin_1),Net-(J6-Pin_4),Net-(J6-Pin_5)</t>
   </si>
   <si>
     <t>10</t>
@@ -556,10 +556,10 @@
     <t>-82.8040</t>
   </si>
   <si>
-    <t>/DTR,GND</t>
-  </si>
-  <si>
-    <t>DTR,GND</t>
+    <t>GND,/DTR</t>
+  </si>
+  <si>
+    <t>DTR</t>
   </si>
   <si>
     <t>12</t>
@@ -616,7 +616,7 @@
     <t>10.1000</t>
   </si>
   <si>
-    <t>Net-(U1-D-),/DTR,Earth,Net-(J4-Pin_4),Net-(J6-Pin_4),/MISO2,Net-(U1-PC0{slash}XTAL2),+5V,VBUS,Net-(J6-Pin_5),/SCK2,Net-(J4-Pin_3),Net-(J3-Pin_2),Net-(U1-XTAL1),Net-(J3-Pin_5),Net-(J6-Pin_3),Net-(J6-Pin_6),Net-(J4-Pin_1),/RESET2,Net-(J3-Pin_3),Net-(J4-Pin_2),Net-(J3-Pin_4),unconnected-(U1-PB0-Pad14),Net-(U1-D+),/RXLED,Net-(J3-Pin_1),Net-(U1-UCAP),Net-(J6-Pin_2),GND,/TXLED,/MOSI2</t>
+    <t>/SCK2,Net-(J4-Pin_2),Net-(J4-Pin_1),Net-(J6-Pin_2),/TXLED,/MOSI2,Net-(U1-UCAP),Net-(U1-D+),unconnected-(U1-PB0-Pad14),Net-(J4-Pin_4),+5V,Net-(J6-Pin_6),Net-(J6-Pin_3),Net-(J3-Pin_2),Net-(J3-Pin_1),/MISO2,Net-(J3-Pin_5),/RXLED,Net-(U1-PC0{slash}XTAL2),Earth,Net-(U1-D-),Net-(U1-XTAL1),Net-(J3-Pin_3),Net-(J3-Pin_4),Net-(J6-Pin_4),Net-(J6-Pin_5),/DTR,VBUS,GND,Net-(J4-Pin_3),/RESET2</t>
   </si>
   <si>
     <t>KiBot Bill of Materials</t>
@@ -649,7 +649,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.6+1</t>
+    <t>9.0.7+1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -694,7 +694,7 @@
     <t>no</t>
   </si>
   <si>
-    <t>GND,Net-(U1-XTAL1)</t>
+    <t>Net-(U1-XTAL1),GND</t>
   </si>
   <si>
     <t>Resettable fuse, polymeric positive temperature coefficient</t>
@@ -724,7 +724,7 @@
     <t>3.4000</t>
   </si>
   <si>
-    <t>VBUS,Net-(J2-VBUS)</t>
+    <t>Net-(J2-VBUS),VBUS</t>
   </si>
   <si>
     <t>Ferrite bead</t>
@@ -742,7 +742,7 @@
     <t>-90.6780</t>
   </si>
   <si>
-    <t>Earth,Net-(J2-Shield)</t>
+    <t>Net-(J2-Shield),Earth</t>
   </si>
   <si>
     <t>Generic connector, double row, 02x02, odd/even pin numbering scheme (row 1 odd numbers, row 2 even numbers), script generated (kicad-library-utils/schlib/autogen/connector/)</t>
@@ -769,7 +769,7 @@
     <t>-95.2500</t>
   </si>
   <si>
-    <t>Net-(J4-Pin_1),Net-(J4-Pin_3),Net-(J4-Pin_4),Net-(J4-Pin_2)</t>
+    <t>Net-(J4-Pin_1),Net-(J4-Pin_3),Net-(J4-Pin_2),Net-(J4-Pin_4)</t>
   </si>
   <si>
     <t>USB Type B connector</t>
@@ -802,7 +802,7 @@
     <t>16.0000</t>
   </si>
   <si>
-    <t>Earth,Net-(J2-VBUS),Net-(J2-D-),Net-(J2-D+),Net-(J2-Shield)</t>
+    <t>Earth,Net-(J2-D-),Net-(J2-D+),Net-(J2-Shield),Net-(J2-VBUS)</t>
   </si>
   <si>
     <t>R1 R2</t>
@@ -832,7 +832,7 @@
     <t>-75.8780</t>
   </si>
   <si>
-    <t>Net-(U1-PC0{slash}XTAL2),Net-(U1-XTAL1)</t>
+    <t>Net-(U1-XTAL1),Net-(U1-PC0{slash}XTAL2)</t>
   </si>
   <si>
     <t>Voltage dependent resistor</t>

--- a/BoM/Positional/t1-bom.xlsx
+++ b/BoM/Positional/t1-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="295">
   <si>
     <t>Row</t>
   </si>
@@ -148,7 +148,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>~</t>
+    <t/>
   </si>
   <si>
     <t>/</t>
@@ -157,9 +157,6 @@
     <t>t1(4)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Excluded from board</t>
   </si>
   <si>
@@ -190,7 +187,7 @@
     <t>1.4000</t>
   </si>
   <si>
-    <t>GND,+5V</t>
+    <t>+5V,GND</t>
   </si>
   <si>
     <t>Default</t>
@@ -289,10 +286,10 @@
     <t>1.7500</t>
   </si>
   <si>
-    <t>/RESET2,+5V</t>
-  </si>
-  <si>
-    <t>RESET2,+5V</t>
+    <t>+5V,/RESET2</t>
+  </si>
+  <si>
+    <t>RESET2</t>
   </si>
   <si>
     <t>5</t>
@@ -325,10 +322,10 @@
     <t>-74.9500</t>
   </si>
   <si>
-    <t>Net-(D2-A),/RXLED</t>
-  </si>
-  <si>
-    <t>RXLED</t>
+    <t>/RXLED,Net-(D2-A)</t>
+  </si>
+  <si>
+    <t>RXLED,Net-(D2-A)</t>
   </si>
   <si>
     <t>6</t>
@@ -367,7 +364,7 @@
     <t>14.0000</t>
   </si>
   <si>
-    <t>,GND,+5V</t>
+    <t>,+5V,GND</t>
   </si>
   <si>
     <t>7</t>
@@ -412,10 +409,7 @@
     <t>6.7800</t>
   </si>
   <si>
-    <t>/SCK2,/MOSI2,GND,/MISO2,+5V,/RESET2</t>
-  </si>
-  <si>
-    <t>RESET2</t>
+    <t>/SCK2,GND,/MOSI2,+5V,/MISO2,/RESET2</t>
   </si>
   <si>
     <t>8</t>
@@ -454,7 +448,7 @@
     <t>11.8600</t>
   </si>
   <si>
-    <t>Net-(J3-Pin_2),Net-(J3-Pin_1),Net-(J3-Pin_3),Net-(J3-Pin_4),Net-(J3-Pin_5)</t>
+    <t>Net-(J3-Pin_2),Net-(J3-Pin_3),Net-(J3-Pin_4),Net-(J3-Pin_5),Net-(J3-Pin_1)</t>
   </si>
   <si>
     <t>9</t>
@@ -487,7 +481,7 @@
     <t>14.4000</t>
   </si>
   <si>
-    <t>Net-(J6-Pin_6),Net-(J6-Pin_2),Net-(J6-Pin_3),Net-(J6-Pin_1),Net-(J6-Pin_4),Net-(J6-Pin_5)</t>
+    <t>Net-(J6-Pin_2),Net-(J6-Pin_3),Net-(J6-Pin_5),Net-(J6-Pin_4),Net-(J6-Pin_6),Net-(J6-Pin_1)</t>
   </si>
   <si>
     <t>10</t>
@@ -556,10 +550,10 @@
     <t>-82.8040</t>
   </si>
   <si>
-    <t>GND,/DTR</t>
-  </si>
-  <si>
-    <t>DTR</t>
+    <t>/DTR,GND</t>
+  </si>
+  <si>
+    <t>DTR,GND</t>
   </si>
   <si>
     <t>12</t>
@@ -616,7 +610,7 @@
     <t>10.1000</t>
   </si>
   <si>
-    <t>/SCK2,Net-(J4-Pin_2),Net-(J4-Pin_1),Net-(J6-Pin_2),/TXLED,/MOSI2,Net-(U1-UCAP),Net-(U1-D+),unconnected-(U1-PB0-Pad14),Net-(J4-Pin_4),+5V,Net-(J6-Pin_6),Net-(J6-Pin_3),Net-(J3-Pin_2),Net-(J3-Pin_1),/MISO2,Net-(J3-Pin_5),/RXLED,Net-(U1-PC0{slash}XTAL2),Earth,Net-(U1-D-),Net-(U1-XTAL1),Net-(J3-Pin_3),Net-(J3-Pin_4),Net-(J6-Pin_4),Net-(J6-Pin_5),/DTR,VBUS,GND,Net-(J4-Pin_3),/RESET2</t>
+    <t>VBUS,Net-(J3-Pin_2),Net-(J3-Pin_3),unconnected-(U1-PB0-Pad14),Net-(J4-Pin_1),Net-(U1-UCAP),/TXLED,Net-(U1-D+),/DTR,Net-(J6-Pin_6),Earth,Net-(U1-D-),/MOSI2,Net-(J6-Pin_5),Net-(J6-Pin_4),Net-(J4-Pin_4),/MISO2,/RXLED,Net-(U1-PC0{slash}XTAL2),Net-(J4-Pin_2),/SCK2,GND,Net-(J6-Pin_3),Net-(J6-Pin_2),Net-(J4-Pin_3),+5V,Net-(U1-XTAL1),Net-(J3-Pin_4),Net-(J3-Pin_5),Net-(J3-Pin_1),/RESET2</t>
   </si>
   <si>
     <t>KiBot Bill of Materials</t>
@@ -649,7 +643,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.7+1</t>
+    <t>10.0.1-10.0.1~ubuntu25.10.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -742,7 +736,7 @@
     <t>-90.6780</t>
   </si>
   <si>
-    <t>Net-(J2-Shield),Earth</t>
+    <t>Earth,Net-(J2-Shield)</t>
   </si>
   <si>
     <t>Generic connector, double row, 02x02, odd/even pin numbering scheme (row 1 odd numbers, row 2 even numbers), script generated (kicad-library-utils/schlib/autogen/connector/)</t>
@@ -802,7 +796,7 @@
     <t>16.0000</t>
   </si>
   <si>
-    <t>Earth,Net-(J2-D-),Net-(J2-D+),Net-(J2-Shield),Net-(J2-VBUS)</t>
+    <t>Net-(J2-VBUS),Net-(J2-Shield),Net-(J2-D+),Net-(J2-D-),Earth</t>
   </si>
   <si>
     <t>R1 R2</t>
@@ -832,7 +826,7 @@
     <t>-75.8780</t>
   </si>
   <si>
-    <t>Net-(U1-XTAL1),Net-(U1-PC0{slash}XTAL2)</t>
+    <t>Net-(U1-PC0{slash}XTAL2),Net-(U1-XTAL1)</t>
   </si>
   <si>
     <t>Voltage dependent resistor</t>
@@ -1465,7 +1459,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="29.7109375" customWidth="1"/>
     <col min="7" max="7" width="46.7109375" customWidth="1"/>
@@ -1494,7 +1488,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1528,13 +1522,13 @@
     </row>
     <row r="2" spans="1:32">
       <c r="C2" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F2" s="3">
         <v>22</v>
@@ -1542,41 +1536,41 @@
     </row>
     <row r="3" spans="1:32">
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1584,13 +1578,13 @@
     </row>
     <row r="6" spans="1:32">
       <c r="C6" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3">
         <v>19</v>
@@ -1738,55 +1732,55 @@
         <v>44</v>
       </c>
       <c r="O9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="Q9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="Q9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R9" s="6" t="s">
+      <c r="S9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="T9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="U9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="V9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="W9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="W9" s="7" t="s">
+      <c r="X9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="X9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y9" s="7" t="s">
+      <c r="Z9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Z9" s="7" t="s">
+      <c r="AA9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AA9" s="7" t="s">
+      <c r="AB9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AB9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC9" s="6" t="s">
+      <c r="AD9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE9" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="AD9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE9" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="AF9" s="7" t="s">
         <v>40</v>
@@ -1794,7 +1788,7 @@
     </row>
     <row r="10" spans="1:32">
       <c r="A10" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>33</v>
@@ -1806,10 +1800,10 @@
         <v>35</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>38</v>
@@ -1833,58 +1827,58 @@
         <v>43</v>
       </c>
       <c r="N10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="S10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="U10" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="V10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="V10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB10" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC10" s="10" t="s">
-        <v>65</v>
-      </c>
       <c r="AD10" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF10" s="11" t="s">
         <v>32</v>
@@ -1892,25 +1886,25 @@
     </row>
     <row r="11" spans="1:32">
       <c r="A11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>39</v>
@@ -1931,58 +1925,58 @@
         <v>43</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="S11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="T11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="T11" s="7" t="s">
+      <c r="U11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="U11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z11" s="7" t="s">
+      <c r="AA11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AA11" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="AB11" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AC11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE11" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="AD11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE11" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="AF11" s="7" t="s">
         <v>32</v>
@@ -1993,25 +1987,25 @@
         <v>40</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="H12" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>32</v>
@@ -2029,58 +2023,58 @@
         <v>43</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="S12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="V12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z12" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="V12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X12" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z12" s="11" t="s">
+      <c r="AA12" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="AA12" s="11" t="s">
-        <v>88</v>
       </c>
       <c r="AB12" s="10" t="s">
         <v>40</v>
       </c>
       <c r="AC12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD12" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="AD12" s="10" t="s">
-        <v>90</v>
-      </c>
       <c r="AE12" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF12" s="11" t="s">
         <v>32</v>
@@ -2088,34 +2082,34 @@
     </row>
     <row r="13" spans="1:32">
       <c r="A13" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="I13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>41</v>
@@ -2127,87 +2121,87 @@
         <v>43</v>
       </c>
       <c r="N13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R13" s="6" t="s">
+      <c r="S13" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="T13" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="T13" s="7" t="s">
+      <c r="U13" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB13" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="U13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB13" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC13" s="6" t="s">
+      <c r="AD13" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AD13" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="AE13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF13" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="AF13" s="7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="30" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F14" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" s="11" t="s">
+      <c r="H14" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>32</v>
@@ -2225,58 +2219,58 @@
         <v>43</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R14" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="S14" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="T14" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="U14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z14" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="U14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="V14" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z14" s="11" t="s">
+      <c r="AA14" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="AA14" s="11" t="s">
+      <c r="AB14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC14" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="AB14" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC14" s="10" t="s">
-        <v>115</v>
-      </c>
       <c r="AD14" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF14" s="11" t="s">
         <v>32</v>
@@ -2284,28 +2278,28 @@
     </row>
     <row r="15" spans="1:32" ht="45" customHeight="1">
       <c r="A15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G15" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>32</v>
@@ -2323,58 +2317,58 @@
         <v>43</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R15" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="S15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="S15" s="7" t="s">
+      <c r="T15" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="T15" s="7" t="s">
+      <c r="U15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="U15" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W15" s="7" t="s">
+      <c r="X15" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z15" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="X15" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z15" s="7" t="s">
+      <c r="AA15" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="AA15" s="7" t="s">
+      <c r="AB15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC15" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="AB15" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC15" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="AD15" s="6" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="AE15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF15" s="7" t="s">
         <v>32</v>
@@ -2382,28 +2376,28 @@
     </row>
     <row r="16" spans="1:32" ht="30" customHeight="1">
       <c r="A16" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="D16" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>137</v>
-      </c>
       <c r="H16" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>32</v>
@@ -2421,58 +2415,58 @@
         <v>43</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R16" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="T16" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="U16" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="V16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X16" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z16" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="AA16" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="V16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="X16" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z16" s="11" t="s">
+      <c r="AB16" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC16" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AA16" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB16" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC16" s="10" t="s">
-        <v>144</v>
-      </c>
       <c r="AD16" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF16" s="11" t="s">
         <v>32</v>
@@ -2480,28 +2474,28 @@
     </row>
     <row r="17" spans="1:32" ht="30" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="D17" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>150</v>
-      </c>
       <c r="H17" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>32</v>
@@ -2519,58 +2513,58 @@
         <v>43</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R17" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="T17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="S17" s="7" t="s">
+      <c r="U17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="X17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA17" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="T17" s="7" t="s">
+      <c r="AB17" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC17" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="U17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="X17" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z17" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA17" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB17" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC17" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="AD17" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AE17" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF17" s="7" t="s">
         <v>32</v>
@@ -2578,28 +2572,28 @@
     </row>
     <row r="18" spans="1:32">
       <c r="A18" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="F18" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="H18" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>32</v>
@@ -2617,58 +2611,58 @@
         <v>43</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R18" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="T18" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="U18" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="T18" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="V18" s="11" t="s">
-        <v>166</v>
-      </c>
       <c r="W18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y18" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="X18" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="Z18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AB18" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AC18" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AD18" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AE18" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AF18" s="11" t="s">
         <v>32</v>
@@ -2676,34 +2670,34 @@
     </row>
     <row r="19" spans="1:32">
       <c r="A19" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>169</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>173</v>
-      </c>
       <c r="I19" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>41</v>
@@ -2715,87 +2709,87 @@
         <v>43</v>
       </c>
       <c r="N19" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="S19" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="O19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R19" s="6" t="s">
+      <c r="T19" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="S19" s="7" t="s">
+      <c r="U19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="V19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB19" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC19" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="T19" s="7" t="s">
+      <c r="AD19" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="U19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z19" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB19" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC19" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AD19" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="AE19" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF19" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:32">
       <c r="A20" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>32</v>
@@ -2813,58 +2807,58 @@
         <v>43</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T20" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="W20" s="11" t="s">
+      <c r="X20" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y20" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="X20" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y20" s="11" t="s">
+      <c r="Z20" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="Z20" s="11" t="s">
+      <c r="AA20" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AA20" s="11" t="s">
-        <v>55</v>
-      </c>
       <c r="AB20" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AC20" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD20" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="AD20" s="10" t="s">
-        <v>90</v>
-      </c>
       <c r="AE20" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF20" s="11" t="s">
         <v>32</v>
@@ -2872,28 +2866,28 @@
     </row>
     <row r="21" spans="1:32" ht="105" customHeight="1">
       <c r="A21" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>32</v>
@@ -2905,64 +2899,64 @@
         <v>41</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R21" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="T21" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="S21" s="7" t="s">
+      <c r="U21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="V21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z21" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="T21" s="7" t="s">
+      <c r="AA21" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB21" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC21" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="U21" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z21" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA21" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="AB21" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="AC21" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="AD21" s="6" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="AE21" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF21" s="7" t="s">
         <v>32</v>
@@ -2986,7 +2980,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="44.7109375" customWidth="1"/>
@@ -3014,7 +3008,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -3048,13 +3042,13 @@
     </row>
     <row r="2" spans="1:32">
       <c r="C2" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F2" s="3">
         <v>22</v>
@@ -3062,41 +3056,41 @@
     </row>
     <row r="3" spans="1:32">
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -3104,13 +3098,13 @@
     </row>
     <row r="6" spans="1:32">
       <c r="C6" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3">
         <v>19</v>
@@ -3228,10 +3222,10 @@
         <v>35</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>38</v>
@@ -3240,13 +3234,13 @@
         <v>39</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>42</v>
@@ -3255,96 +3249,96 @@
         <v>43</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="Q9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="Q9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="S9" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y9" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="Z9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="U9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y9" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC9" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="AD9" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF9" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="AF9" s="7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:32">
       <c r="A10" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>229</v>
-      </c>
       <c r="H10" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L10" s="12" t="s">
         <v>42</v>
@@ -3353,58 +3347,58 @@
         <v>43</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R10" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z10" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="AA10" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="T10" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="V10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z10" s="11" t="s">
+      <c r="AB10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="AA10" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="AB10" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC10" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="AD10" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF10" s="11" t="s">
         <v>32</v>
@@ -3412,37 +3406,37 @@
     </row>
     <row r="11" spans="1:32">
       <c r="A11" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>42</v>
@@ -3451,58 +3445,58 @@
         <v>43</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="W11" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="X11" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AA11" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="AB11" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AD11" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AE11" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF11" s="7" t="s">
         <v>32</v>
@@ -3513,34 +3507,34 @@
         <v>40</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>245</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L12" s="12" t="s">
         <v>42</v>
@@ -3549,58 +3543,58 @@
         <v>43</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R12" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="T12" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="S12" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="T12" s="11" t="s">
-        <v>248</v>
-      </c>
       <c r="U12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="V12" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="W12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X12" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y12" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z12" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="X12" s="10" t="s">
+      <c r="AA12" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z12" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA12" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="AB12" s="10" t="s">
         <v>40</v>
       </c>
       <c r="AC12" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AD12" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF12" s="11" t="s">
         <v>32</v>
@@ -3608,37 +3602,37 @@
     </row>
     <row r="13" spans="1:32">
       <c r="A13" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="F13" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="I13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>42</v>
@@ -3647,58 +3641,58 @@
         <v>43</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R13" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="T13" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="U13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z13" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="T13" s="7" t="s">
+      <c r="AA13" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="U13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="X13" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y13" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z13" s="7" t="s">
+      <c r="AB13" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC13" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="AA13" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB13" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC13" s="6" t="s">
-        <v>260</v>
-      </c>
       <c r="AD13" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AE13" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF13" s="7" t="s">
         <v>32</v>
@@ -3706,37 +3700,37 @@
     </row>
     <row r="14" spans="1:32">
       <c r="A14" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L14" s="12" t="s">
         <v>42</v>
@@ -3745,96 +3739,96 @@
         <v>43</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="P14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="Q14" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S14" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC14" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="T14" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="V14" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z14" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA14" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB14" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC14" s="10" t="s">
-        <v>265</v>
-      </c>
       <c r="AD14" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AE14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF14" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="AF14" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:32">
       <c r="A15" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>42</v>
@@ -3843,58 +3837,58 @@
         <v>43</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S15" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC15" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="T15" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W15" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y15" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB15" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC15" s="6" t="s">
-        <v>270</v>
-      </c>
       <c r="AD15" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AE15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF15" s="7" t="s">
         <v>32</v>
@@ -3902,37 +3896,37 @@
     </row>
     <row r="16" spans="1:32">
       <c r="A16" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>275</v>
-      </c>
       <c r="H16" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L16" s="12" t="s">
         <v>42</v>
@@ -3941,96 +3935,96 @@
         <v>43</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="P16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="Q16" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R16" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="T16" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="U16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z16" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="AA16" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="U16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="V16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z16" s="11" t="s">
+      <c r="AB16" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC16" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="AA16" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB16" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC16" s="10" t="s">
-        <v>281</v>
-      </c>
       <c r="AD16" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AE16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF16" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="AF16" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:32">
       <c r="A17" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>286</v>
-      </c>
       <c r="H17" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>32</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>42</v>
@@ -4039,58 +4033,58 @@
         <v>43</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R17" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="T17" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="S17" s="7" t="s">
+      <c r="U17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y17" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z17" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="T17" s="7" t="s">
+      <c r="AA17" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="U17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="X17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y17" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z17" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="AA17" s="7" t="s">
-        <v>291</v>
-      </c>
       <c r="AB17" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AD17" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AE17" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF17" s="7" t="s">
         <v>32</v>
@@ -4116,27 +4110,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
